--- a/ScrapSystem.Web/obj/Release/net8.0/PubTmp/Out/wwwroot/files/Huongdansudung.xlsx
+++ b/ScrapSystem.Web/obj/Release/net8.0/PubTmp/Out/wwwroot/files/Huongdansudung.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Ban Giao\Tuan Anh\scrap\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70K6885\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC38997-0EB5-492B-8EDC-7F2768CFC76F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669DC30A-13B9-46FC-BAA5-3CFDA690A6E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-810" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Doucument Mobile" sheetId="2" r:id="rId1"/>
+    <sheet name="Web Report" sheetId="3" r:id="rId1"/>
+    <sheet name="Doucument Mobile" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,12 +30,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Hướng dẫn sử dụng phần mềm trên thiết bị PDA</t>
   </si>
@@ -82,6 +86,36 @@
   </si>
   <si>
     <t>8. Form xóa dữ liệu tháng cũ trên thiết bị mobile</t>
+  </si>
+  <si>
+    <t>Hướng dẫn sử dụng Chức năng trên web</t>
+  </si>
+  <si>
+    <t>2. Menu chính</t>
+  </si>
+  <si>
+    <t>Scrap List Management</t>
+  </si>
+  <si>
+    <t>Hệ thống phê duyệt điện tử E - Issue in out trên Portal</t>
+  </si>
+  <si>
+    <t>Upload scrap list theo format chung</t>
+  </si>
+  <si>
+    <t>Print pallet list</t>
+  </si>
+  <si>
+    <t>3. Setting mater</t>
+  </si>
+  <si>
+    <t>4. Báo cáo sau khi chụp ảnh hàng hủy</t>
+  </si>
+  <si>
+    <t>1. Login trên Portal</t>
+  </si>
+  <si>
+    <t>Tool convert scarp for PUS</t>
   </si>
 </sst>
 </file>
@@ -155,6 +189,3796 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>225878</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>476463</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>152586</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3ED8B598-2E03-4A82-9504-9B3A9C1C0CF3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1445078" y="933450"/>
+          <a:ext cx="2079385" cy="1819461"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>353030</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA745749-BF7F-43C8-9A4C-E6E6D96E5484}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4552950" y="685800"/>
+          <a:ext cx="4334480" cy="3038475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>86898</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>48179</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0179147-764F-4B2D-BE1E-071CDEC4CFD7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1438275" y="4200525"/>
+          <a:ext cx="8402223" cy="3972479"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectangle 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E83069A7-F25A-41CB-A105-14E89574DB38}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1552575" y="1895475"/>
+          <a:ext cx="1552575" cy="342900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Arrow: Right 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC36E44F-F569-4922-A3FD-7ABE255FF707}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3895725" y="1752600"/>
+          <a:ext cx="400050" cy="762000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>104776</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>171451</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Oval 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D64EE264-C3C6-4D2B-88AC-C0D44EB54510}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2543176" y="5486401"/>
+          <a:ext cx="295274" cy="266699"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>85726</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Oval 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12731D8F-266D-4004-83D2-A8EC78CF4269}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2524126" y="5772151"/>
+          <a:ext cx="295274" cy="266699"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>2</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>276226</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>142876</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Oval 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2874287-0B51-498F-8C5B-00C1140B098E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2714626" y="6029326"/>
+          <a:ext cx="295274" cy="266699"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>3</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>171451</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>57151</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Oval 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4127AB9D-358D-4955-9807-809773302903}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2609851" y="6324601"/>
+          <a:ext cx="295274" cy="266699"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>4</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419099</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Oval 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9E05D44-F6D7-454F-8B19-5A3E57B0BA31}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="123825" y="8524875"/>
+          <a:ext cx="295274" cy="266699"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{521C1531-F11D-4B95-B73D-2FE6A49F1387}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="676275" y="9029699"/>
+          <a:ext cx="13134975" cy="4324351"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Rectangle 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E1F6A6B-FDC4-4CC4-BE49-39EC187C249A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10067925" y="9782175"/>
+          <a:ext cx="2990850" cy="628650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>47626</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>104774</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Speech Bubble: Rectangle with Corners Rounded 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5305D08B-4F17-4127-A970-1D014E26772C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10410826" y="8867774"/>
+          <a:ext cx="1323974" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -21543"/>
+            <a:gd name="adj2" fmla="val 131103"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>upload</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> mẫu theo 2 loại file của PUS</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>276224</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Rectangle 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{057ACAFB-0A81-4F30-B9A9-75901A07501A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685799" y="10458450"/>
+          <a:ext cx="11172825" cy="552449"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>180974</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>361949</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Speech Bubble: Rectangle with Corners Rounded 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39F0B6EE-E223-4FC6-A7D8-0D0FB7364E9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12077700" y="10496549"/>
+          <a:ext cx="1695449" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -66147"/>
+            <a:gd name="adj2" fmla="val -10167"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Cấu</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> hình theo format tool nếu có thay đổi cột dữ liệu</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Rectangle 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D59EA8E0-F975-40E1-8DC4-76CFE44D5ED7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13315950" y="11630025"/>
+          <a:ext cx="476250" cy="1790700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Speech Bubble: Rectangle with Corners Rounded 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93921984-14F1-4597-B317-8CA8FFB30D6C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14097000" y="10601325"/>
+          <a:ext cx="1171575" cy="1200149"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -78269"/>
+            <a:gd name="adj2" fmla="val 51738"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Có</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> thể chỉnh lại số lượng nếu sai, hoặc cập nhật thêm thông tin</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>152401</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Speech Bubble: Rectangle with Corners Rounded 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FF82ED3-D6F5-40C4-ACBA-489A7AA7003B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6858001" y="8515350"/>
+          <a:ext cx="2238374" cy="781049"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -21543"/>
+            <a:gd name="adj2" fmla="val 131103"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Bộ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> phận mang hủy hàng cần dowload mẫu scrap list chung để nhập số pallet mang đi hủy</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>438149</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Oval 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E192004-E986-4E11-9018-3C7EE5552519}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="142875" y="13525500"/>
+          <a:ext cx="295274" cy="266699"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>2</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>47624</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>402868</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Picture 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1F55723-95A3-46D6-98CA-04E3CEC9C2F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="657224" y="13992225"/>
+          <a:ext cx="13156844" cy="3771900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95249</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="Speech Bubble: Rectangle with Corners Rounded 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14AB3068-C89F-40AB-A501-6DBA1C06767A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6191249" y="14106525"/>
+          <a:ext cx="1228726" cy="685799"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 16441"/>
+            <a:gd name="adj2" fmla="val 84626"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Export</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> mẫu dispostion cho các bộ phần cần </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>171449</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Speech Bubble: Rectangle with Corners Rounded 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D511FB5-1265-4610-86E6-8CE10BBBF7F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8096249" y="14106525"/>
+          <a:ext cx="1228726" cy="685799"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 16441"/>
+            <a:gd name="adj2" fmla="val 84626"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Export</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> mẫu Scrap list theo format chung</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>466724</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="Speech Bubble: Rectangle with Corners Rounded 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17855B34-32A3-413B-B8B4-65557F9C8B81}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9610724" y="13706476"/>
+          <a:ext cx="1914526" cy="1076324"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -17887"/>
+            <a:gd name="adj2" fmla="val 75776"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Confirm</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> E-IssueOut Form A &amp; Form B cho kế toán. Áp dụng ký điện tử theo các Issue out được tạo ra bên hệ thống ký điện tử</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="Rectangle 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27D272EA-C4C7-42C1-8E33-67A5CB74DFB5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13192125" y="16297275"/>
+          <a:ext cx="476250" cy="1400175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>352424</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="Speech Bubble: Rectangle with Corners Rounded 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34D16C99-0566-47D0-9B76-85B1ACE3D35E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13763624" y="15630525"/>
+          <a:ext cx="1362076" cy="1104900"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -59678"/>
+            <a:gd name="adj2" fmla="val 27103"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Bộ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> phận có thể chỉnh sửa lại thông tin trước khi mang hàng đi hủy. chụp ảnh</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="Rectangle 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2FD8F2D-E833-43E5-96C7-1B2B9B6B550C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11296650" y="16316325"/>
+          <a:ext cx="476250" cy="1400175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>533399</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Speech Bubble: Rectangle with Corners Rounded 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2218B01F-0CB4-4D95-A8C1-F4F42CC400EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11506199" y="14668500"/>
+          <a:ext cx="1133476" cy="1104900"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -29608"/>
+            <a:gd name="adj2" fmla="val 94344"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Trạng</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> thái phê duyệt điện tử của bộ phận cần xin chữ ký</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>295274</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>95249</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="Picture 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E235497B-D6FF-4586-96D3-D7E32399DA5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3952874" y="19011900"/>
+          <a:ext cx="1628775" cy="1571625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="Picture 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97D52EE3-0534-4913-84F2-07578600B43D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7439025" y="18497550"/>
+          <a:ext cx="4038600" cy="3305175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="Rectangle 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26592F78-010F-4FEB-BAAC-4D4EDBEB2252}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3933825" y="20259675"/>
+          <a:ext cx="1552575" cy="342900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="Arrow: Right 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67F5B410-0E76-4F7B-8120-AF634208F73C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6343650" y="19631025"/>
+          <a:ext cx="400050" cy="762000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="Picture 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7185FAA3-4A88-4081-BFD5-6FAD3DE39358}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1743075" y="22336125"/>
+          <a:ext cx="14535150" cy="5715000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="Arrow: Right 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B82A9A97-244C-4346-BF70-EFD5F4F781A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="8939212" y="21731288"/>
+          <a:ext cx="257175" cy="762000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>123824</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="Rectangle 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB768C86-43CE-4545-8771-99625FF8DDA0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8658224" y="23317200"/>
+          <a:ext cx="7019926" cy="1400175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>123826</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="Speech Bubble: Rectangle with Corners Rounded 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D04974F9-6B5B-46E3-8EDA-F384D20653D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11639550" y="22012275"/>
+          <a:ext cx="1285876" cy="1104900"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -47897"/>
+            <a:gd name="adj2" fmla="val 109000"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Hệ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> thống sẽ gồm 9 chữ ký phê duyệt thay vì phê duyệt giấy tờ.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>523874</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>66674</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="Oval 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8803250A-182D-42D9-B128-8396A4F57BAA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="228600" y="28260675"/>
+          <a:ext cx="295274" cy="361949"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>3</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>164</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Picture 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{294A8356-C8C4-4D60-9433-0F2CE095EEAC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6981825" y="28613100"/>
+          <a:ext cx="9486900" cy="3067050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>157</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="Oval 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66813852-D138-45E7-A5C1-1F05D2482ED6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7639050" y="30308550"/>
+          <a:ext cx="295274" cy="361949"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>3</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>161924</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="41" name="Picture 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{808DBA94-5EC7-4A6B-814E-7359C10833AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="152400" y="28717874"/>
+          <a:ext cx="5638800" cy="2428875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="Arrow: Right 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49216E5E-EF9A-4B9F-A4EE-A2462CA9D1BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6238875" y="30108525"/>
+          <a:ext cx="314325" cy="771525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>166</xdr:row>
+      <xdr:rowOff>104774</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>189</xdr:row>
+      <xdr:rowOff>48475</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="43" name="Picture 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00A34C0D-CE58-44C3-96C4-C3E67A494F9E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="828675" y="32137349"/>
+          <a:ext cx="7953375" cy="4325201"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>164</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>485774</xdr:colOff>
+      <xdr:row>166</xdr:row>
+      <xdr:rowOff>38098</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="Oval 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BEA71A5-D855-4E85-BCAE-BFAEC72ABDDC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="190500" y="31775400"/>
+          <a:ext cx="295274" cy="295273"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>4</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>173</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>104773</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="Oval 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72503C5B-4261-421B-80AA-4A5A59ACB5C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1362075" y="33385125"/>
+          <a:ext cx="209550" cy="276223"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>4</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>439299</xdr:colOff>
+      <xdr:row>187</xdr:row>
+      <xdr:rowOff>57663</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Picture 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F3E897D-81B0-4CA7-97AE-5F18C4F29301}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9925050" y="32413575"/>
+          <a:ext cx="7583049" cy="3677163"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>164</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="Speech Bubble: Rectangle with Corners Rounded 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A25DCBE4-AA0A-47A5-90D8-006C00A31C1D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7267575" y="31765875"/>
+          <a:ext cx="1285876" cy="1104900"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -26416"/>
+            <a:gd name="adj2" fmla="val 94345"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Chọn</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> sanction và pallet cần in ra dan vào khu vực pallelt cần hủy để chụp ảnh</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>175</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>180</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="Arrow: Right 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27120082-88D1-480B-BCE2-6106674548D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9124950" y="33794700"/>
+          <a:ext cx="390525" cy="923925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>193</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>431112</xdr:colOff>
+      <xdr:row>211</xdr:row>
+      <xdr:rowOff>76688</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Picture 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0450E24-E79E-4485-BFAD-79BC224E4AD0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="647700" y="37233225"/>
+          <a:ext cx="15633012" cy="3496163"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>199</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123824</xdr:colOff>
+      <xdr:row>211</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="Rectangle 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B251BA13-0378-49FD-8AE5-67721E1B5A8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685799" y="38481000"/>
+          <a:ext cx="1266825" cy="2276475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>133351</xdr:colOff>
+      <xdr:row>204</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>208</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="Speech Bubble: Rectangle 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04F1EF0D-3866-4B82-A065-DD1C88B6760A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1962151" y="39376350"/>
+          <a:ext cx="942974" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -65257"/>
+            <a:gd name="adj2" fmla="val -16768"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Danh sách các</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> mater cần setting</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>215</xdr:row>
+      <xdr:rowOff>38099</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>235</xdr:row>
+      <xdr:rowOff>162586</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Picture 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C379112C-E25B-4541-94E6-14B37E83353D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="628650" y="41452799"/>
+          <a:ext cx="15640050" cy="3934487"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>171449</xdr:colOff>
+      <xdr:row>223</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>257174</xdr:colOff>
+      <xdr:row>226</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="Speech Bubble: Rectangle 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEBB8FA6-167E-4806-8334-BF7ABAD7522A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2000249" y="42995849"/>
+          <a:ext cx="1304925" cy="647701"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -21713"/>
+            <a:gd name="adj2" fmla="val 83318"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Show ảnh</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> cần chụp theo số pallet</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>218</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>219074</xdr:colOff>
+      <xdr:row>221</xdr:row>
+      <xdr:rowOff>47623</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="Speech Bubble: Rectangle 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69AD9AEE-A1D0-4D30-8003-7A4BB35FDE12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9639300" y="42157649"/>
+          <a:ext cx="942974" cy="495299"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -29904"/>
+            <a:gd name="adj2" fmla="val 96553"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Chọn</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> sacntion</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>239</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>266</xdr:row>
+      <xdr:rowOff>153263</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Picture 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49708918-B804-45E2-AEF7-431EED6DD46F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="619125" y="46215300"/>
+          <a:ext cx="8829675" cy="5115788"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>237</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>238</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="Arrow: Down 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA1C2D1D-8AA7-40D6-BD7E-214F343D43B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1619250" y="45672375"/>
+          <a:ext cx="1504950" cy="314325"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>262</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>265</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="57" name="Rectangle 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE154C78-9C2E-45B6-81AE-265A1DB92A12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7419975" y="50587275"/>
+          <a:ext cx="1743075" cy="485775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>438151</xdr:colOff>
+      <xdr:row>260</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>400051</xdr:colOff>
+      <xdr:row>264</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="58" name="Speech Bubble: Rectangle 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02B90671-9A45-4CEC-AFC7-7A73659863BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9582151" y="50187225"/>
+          <a:ext cx="1181100" cy="647701"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -83757"/>
+            <a:gd name="adj2" fmla="val 27436"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Show ảnh</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> chụp theo .pdf và dowload khi cần</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>237</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>553720</xdr:colOff>
+      <xdr:row>268</xdr:row>
+      <xdr:rowOff>48895</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99263854-8F1A-4F08-AD7C-7C38B0AC89C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11020425" y="45672375"/>
+          <a:ext cx="6602095" cy="5935345"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>461963</xdr:colOff>
+      <xdr:row>247</xdr:row>
+      <xdr:rowOff>138113</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>166688</xdr:colOff>
+      <xdr:row>255</xdr:row>
+      <xdr:rowOff>119063</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="60" name="Arrow: Down 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29BB97CE-9BB0-401D-AA43-849A6D99F55E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="9620251" y="48291750"/>
+          <a:ext cx="1504950" cy="314325"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -7093,6 +10917,67 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25F19114-F5D1-469C-8AE5-AF7CFC3875A0}">
+  <dimension ref="A1:D214"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.35">
+      <c r="D1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B71" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B94" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B148" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B166" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A192" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A214" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BF85636-EFC7-4369-B8CE-862E286B766F}">
   <dimension ref="A2:N271"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
